--- a/outputs/webpage-feature-status/FEATURE_STATUS.xlsx
+++ b/outputs/webpage-feature-status/FEATURE_STATUS.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R10900674913d49c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Status" sheetId="2" r:id="Re2d1b1e935684d6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="3" r:id="R5d019d403a7b46b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Runs" sheetId="4" r:id="R922b0588e6664c18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R61459c308e8845c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R8627e79d76644519"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Status" sheetId="2" r:id="Rf27e1b856183414c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="3" r:id="R5bd84497de014a4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Runs" sheetId="4" r:id="R8c8edc8280574a13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" r:id="R72292e619e9146b6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -288,7 +288,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefectLogTable" displayName="DefectLogTable" ref="A4:N11" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DefectLogTable" displayName="DefectLogTable" ref="A4:N14" headerRowCount="1">
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="Defect ID"/>
     <x:tableColumn id="2" name="Feature ID(s)"/>
@@ -310,7 +310,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TestRunsTable" displayName="TestRunsTable" ref="A4:G7" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TestRunsTable" displayName="TestRunsTable" ref="A4:G10" headerRowCount="1">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Run ID"/>
     <x:tableColumn id="2" name="Date"/>
@@ -530,7 +530,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="4" t="str">
-        <x:v>Canonical feature/user-story tracker for /Users/tiankaixie/Local/webpage. Updated through code inventory and baseline build on 2026-06-29.</x:v>
+        <x:v>Canonical feature/user-story tracker for /Users/tiankaixie/Local/webpage. Updated through final browser regression on 2026-06-29.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -556,7 +556,7 @@
       </x:c>
       <x:c r="B6" s="18" t="n">
         <x:f>COUNTIF('Feature Status'!$I$5:$I$47,"Not Tested")</x:f>
-        <x:v>29</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -573,8 +573,8 @@
         <x:v>Open defects</x:v>
       </x:c>
       <x:c r="B8" s="18" t="n">
-        <x:f>COUNTIF('Defect Log'!$E$5:$E$11,"Open")</x:f>
-        <x:v>7</x:v>
+        <x:f>COUNTIF('Defect Log'!$E$5:$E$14,"Open")</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -582,16 +582,16 @@
         <x:v>High/critical open defects</x:v>
       </x:c>
       <x:c r="B9" s="18" t="n">
-        <x:f>COUNTIFS('Defect Log'!$E$5:$E$11,"Open",'Defect Log'!$C$5:$C$11,"High")+COUNTIFS('Defect Log'!$E$5:$E$11,"Open",'Defect Log'!$C$5:$C$11,"Critical")</x:f>
-        <x:v>1</x:v>
+        <x:f>COUNTIFS('Defect Log'!$E$5:$E$14,"Open",'Defect Log'!$C$5:$C$14,"High")+COUNTIFS('Defect Log'!$E$5:$E$14,"Open",'Defect Log'!$C$5:$C$14,"Critical")</x:f>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="17" t="str">
-        <x:v>Baseline commit</x:v>
+        <x:v>Fix range</x:v>
       </x:c>
       <x:c r="B10" s="18" t="str">
-        <x:v>05cdd87</x:v>
+        <x:v>8e2c78a..30d3343</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -607,7 +607,7 @@
         <x:v>Next phase</x:v>
       </x:c>
       <x:c r="B12" s="20" t="str">
-        <x:v>Browser QA: desktop/mobile/light/dark for every user story</x:v>
+        <x:v>User review / optional deploy</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -723,7 +723,7 @@
         <x:v>Load representative pages; inspect title/meta/canonical/OG fields; confirm no broken icon/manifest/RSS references.</x:v>
       </x:c>
       <x:c r="I5" s="25" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J5" s="25" t="str">
         <x:v>High</x:v>
@@ -732,10 +732,14 @@
       <x:c r="L5" s="25" t="str">
         <x:v>No Fix Needed</x:v>
       </x:c>
-      <x:c r="M5" s="28" t="str"/>
-      <x:c r="N5" s="25" t="str"/>
+      <x:c r="M5" s="28" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N5" s="25" t="str">
+        <x:v>Representative production routes expose correct titles; manifest/RSS/icons linked; link crawl found 0 broken local refs.</x:v>
+      </x:c>
       <x:c r="O5" s="16" t="str">
-        <x:v>Important for public/social discovery.</x:v>
+        <x:v>Public/social discovery metadata is now aligned with TK site identity.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -764,7 +768,7 @@
         <x:v>Tab from page start; verify skip link appears and focuses main content.</x:v>
       </x:c>
       <x:c r="I6" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J6" s="26" t="str">
         <x:v>Medium</x:v>
@@ -773,9 +777,15 @@
       <x:c r="L6" s="26" t="str">
         <x:v>No Fix Needed</x:v>
       </x:c>
-      <x:c r="M6" s="29" t="str"/>
-      <x:c r="N6" s="26" t="str"/>
-      <x:c r="O6" s="18" t="str"/>
+      <x:c r="M6" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N6" s="26" t="str">
+        <x:v>DOM structure check: a[href="#main"] with text "Skip to content" and main#main target both present.</x:v>
+      </x:c>
+      <x:c r="O6" s="18" t="str">
+        <x:v>Keyboard Tab simulation in the browser harness was unreliable, so structural accessibility was verified directly.</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="17" t="str">
@@ -803,7 +813,7 @@
         <x:v>Click theme switch on home and internal pages; reload/navigate; verify text, colors, localStorage, and aria state.</x:v>
       </x:c>
       <x:c r="I7" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J7" s="26" t="str">
         <x:v>High</x:v>
@@ -812,8 +822,12 @@
       <x:c r="L7" s="26" t="str">
         <x:v>No Fix Needed</x:v>
       </x:c>
-      <x:c r="M7" s="29" t="str"/>
-      <x:c r="N7" s="26" t="str"/>
+      <x:c r="M7" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N7" s="26" t="str">
+        <x:v>Theme switch toggled light -&gt; dark, aria state updated, and dark state persisted after reload.</x:v>
+      </x:c>
       <x:c r="O7" s="18" t="str"/>
     </x:row>
     <x:row r="8">
@@ -842,7 +856,7 @@
         <x:v>Visit Blog, Projects, Music, Changelog; verify nav contents, links, focus states, and mobile layout.</x:v>
       </x:c>
       <x:c r="I8" s="26" t="str">
-        <x:v>Needs Browser Verification</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J8" s="26" t="str">
         <x:v>High</x:v>
@@ -851,12 +865,16 @@
         <x:v>D004</x:v>
       </x:c>
       <x:c r="L8" s="26" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="M8" s="29" t="str"/>
-      <x:c r="N8" s="26" t="str"/>
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="M8" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N8" s="26" t="str">
+        <x:v>Nav verified on home and internal pages: BLOG/PROJECTS/MUSIC/CHANGELOG/SEARCH where intended; no desktop/mobile overflow.</x:v>
+      </x:c>
       <x:c r="O8" s="18" t="str">
-        <x:v>Config includes Music, Changelog, and Search, but custom NavBar currently only renders Blog/Projects/theme.</x:v>
+        <x:v>Fixed by 0623cc8.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -885,7 +903,7 @@
         <x:v>Navigate between pages using links; verify progress bar appears and clears without console errors.</x:v>
       </x:c>
       <x:c r="I9" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J9" s="26" t="str">
         <x:v>Low</x:v>
@@ -894,8 +912,12 @@
       <x:c r="L9" s="26" t="str">
         <x:v>No Fix Needed</x:v>
       </x:c>
-      <x:c r="M9" s="29" t="str"/>
-      <x:c r="N9" s="26" t="str"/>
+      <x:c r="M9" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N9" s="26" t="str">
+        <x:v>15 production route states navigated with no console warning/error and no stuck transition UI.</x:v>
+      </x:c>
       <x:c r="O9" s="18" t="str"/>
     </x:row>
     <x:row r="10">
@@ -924,7 +946,7 @@
         <x:v>Open article with images; click image; verify zoom overlay opens and closes.</x:v>
       </x:c>
       <x:c r="I10" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J10" s="26" t="str">
         <x:v>Low</x:v>
@@ -933,9 +955,15 @@
       <x:c r="L10" s="26" t="str">
         <x:v>No Fix Needed</x:v>
       </x:c>
-      <x:c r="M10" s="29" t="str"/>
-      <x:c r="N10" s="26" t="str"/>
-      <x:c r="O10" s="18" t="str"/>
+      <x:c r="M10" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N10" s="26" t="str">
+        <x:v>Prose/article route loaded cleanly with medium-zoom hook present; current public article has no image fixture to open.</x:v>
+      </x:c>
+      <x:c r="O10" s="18" t="str">
+        <x:v>No user-visible image zoom defect in current content.</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="str">
@@ -963,7 +991,7 @@
         <x:v>Scroll article/list pages; click button; verify smooth return to top and no overlay conflicts.</x:v>
       </x:c>
       <x:c r="I11" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J11" s="26" t="str">
         <x:v>Medium</x:v>
@@ -972,8 +1000,12 @@
       <x:c r="L11" s="26" t="str">
         <x:v>No Fix Needed</x:v>
       </x:c>
-      <x:c r="M11" s="29" t="str"/>
-      <x:c r="N11" s="26" t="str"/>
+      <x:c r="M11" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N11" s="26" t="str">
+        <x:v>Article scrollY 1180 -&gt; 0 after clicking #to-top-button.</x:v>
+      </x:c>
       <x:c r="O11" s="18" t="str"/>
     </x:row>
     <x:row r="12">
@@ -1002,7 +1034,7 @@
         <x:v>Open homepage desktop/mobile in light/dark; verify identity header and theme switch are visible and aligned.</x:v>
       </x:c>
       <x:c r="I12" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J12" s="26" t="str">
         <x:v>High</x:v>
@@ -1011,10 +1043,14 @@
       <x:c r="L12" s="26" t="str">
         <x:v>No Fix Needed</x:v>
       </x:c>
-      <x:c r="M12" s="29" t="str"/>
-      <x:c r="N12" s="26" t="str"/>
+      <x:c r="M12" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N12" s="26" t="str">
+        <x:v>Homepage identity header rendered as TIANKAI XIE on desktop/mobile; theme switch visible and aligned.</x:v>
+      </x:c>
       <x:c r="O12" s="18" t="str">
-        <x:v>Must match experimental black/white editorial style.</x:v>
+        <x:v>Black/white editorial direction preserved.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1043,7 +1079,7 @@
         <x:v>Click each internal/external link; verify correct destination and safe external behavior.</x:v>
       </x:c>
       <x:c r="I13" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J13" s="26" t="str">
         <x:v>High</x:v>
@@ -1052,8 +1088,12 @@
       <x:c r="L13" s="26" t="str">
         <x:v>No Fix Needed</x:v>
       </x:c>
-      <x:c r="M13" s="29" t="str"/>
-      <x:c r="N13" s="26" t="str"/>
+      <x:c r="M13" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N13" s="26" t="str">
+        <x:v>Homepage exposes email plus Google Scholar, GitHub, X, Instagram, LinkedIn, and /cv.pdf links.</x:v>
+      </x:c>
       <x:c r="O13" s="18" t="str"/>
     </x:row>
     <x:row r="14">
@@ -1082,7 +1122,7 @@
         <x:v>Read homepage on desktop/mobile; verify hierarchy, line length, and dark/light contrast.</x:v>
       </x:c>
       <x:c r="I14" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J14" s="26" t="str">
         <x:v>High</x:v>
@@ -1091,8 +1131,12 @@
       <x:c r="L14" s="26" t="str">
         <x:v>No Fix Needed</x:v>
       </x:c>
-      <x:c r="M14" s="29" t="str"/>
-      <x:c r="N14" s="26" t="str"/>
+      <x:c r="M14" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N14" s="26" t="str">
+        <x:v>Homepage MANIFESTO and Diamond Sutra quote rendered with readable hierarchy and no overflow.</x:v>
+      </x:c>
       <x:c r="O14" s="18" t="str"/>
     </x:row>
     <x:row r="15">
@@ -1121,7 +1165,7 @@
         <x:v>Load homepage; verify video displays, autoplays muted, does not overflow, and degrades acceptably if asset fails.</x:v>
       </x:c>
       <x:c r="I15" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J15" s="26" t="str">
         <x:v>High</x:v>
@@ -1130,8 +1174,12 @@
       <x:c r="L15" s="26" t="str">
         <x:v>No Fix Needed</x:v>
       </x:c>
-      <x:c r="M15" s="29" t="str"/>
-      <x:c r="N15" s="26" t="str"/>
+      <x:c r="M15" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N15" s="26" t="str">
+        <x:v>Homepage video/source elements present; desktop/mobile layout has no overflow.</x:v>
+      </x:c>
       <x:c r="O15" s="18" t="str"/>
     </x:row>
     <x:row r="16">
@@ -1160,18 +1208,24 @@
         <x:v>Compare 1440px, 1024px, 390px; verify no horizontal overflow, clipped text, or awkward stacking.</x:v>
       </x:c>
       <x:c r="I16" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J16" s="26" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="K16" s="26" t="str"/>
       <x:c r="L16" s="26" t="str">
-        <x:v>No Fix Needed</x:v>
-      </x:c>
-      <x:c r="M16" s="29" t="str"/>
-      <x:c r="N16" s="26" t="str"/>
-      <x:c r="O16" s="18" t="str"/>
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="M16" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N16" s="26" t="str">
+        <x:v>Homepage grid verified at 1280px as 384px / 384px / 384px and mobile 390px without horizontal overflow.</x:v>
+      </x:c>
+      <x:c r="O16" s="18" t="str">
+        <x:v>Fixed Astro class/className issue by 8e2c78a.</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="17" t="str">
@@ -1199,7 +1253,7 @@
         <x:v>Open /blog/; verify post list, date formatting, links, empty state behavior, and responsive layout.</x:v>
       </x:c>
       <x:c r="I17" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J17" s="26" t="str">
         <x:v>High</x:v>
@@ -1208,8 +1262,12 @@
       <x:c r="L17" s="26" t="str">
         <x:v>No Fix Needed</x:v>
       </x:c>
-      <x:c r="M17" s="29" t="str"/>
-      <x:c r="N17" s="26" t="str"/>
+      <x:c r="M17" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N17" s="26" t="str">
+        <x:v>/blog/ renders the current post list and links to Setting up Remote Server Development Environment.</x:v>
+      </x:c>
       <x:c r="O17" s="18" t="str"/>
     </x:row>
     <x:row r="18">
@@ -1238,18 +1296,24 @@
         <x:v>Open article; verify metadata, content styling, links, code blocks, images, date/read-time display, and no console errors.</x:v>
       </x:c>
       <x:c r="I18" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J18" s="26" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="K18" s="26" t="str"/>
       <x:c r="L18" s="26" t="str">
-        <x:v>No Fix Needed</x:v>
-      </x:c>
-      <x:c r="M18" s="29" t="str"/>
-      <x:c r="N18" s="26" t="str"/>
-      <x:c r="O18" s="18" t="str"/>
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="M18" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N18" s="26" t="str">
+        <x:v>Article detail route verified: title, body, code blocks, TOC, share link, and cleaned public copy all render without console errors.</x:v>
+      </x:c>
+      <x:c r="O18" s="18" t="str">
+        <x:v>Copy cleanup fixed by 30d3343.</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="17" t="str">
@@ -1277,7 +1341,7 @@
         <x:v>Open article/list with TOC; test desktop hover/active highlight; test mobile open, link close, backdrop layering.</x:v>
       </x:c>
       <x:c r="I19" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J19" s="26" t="str">
         <x:v>High</x:v>
@@ -1286,8 +1350,12 @@
       <x:c r="L19" s="26" t="str">
         <x:v>No Fix Needed</x:v>
       </x:c>
-      <x:c r="M19" s="29" t="str"/>
-      <x:c r="N19" s="26" t="str"/>
+      <x:c r="M19" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N19" s="26" t="str">
+        <x:v>Mobile TOC opened with backdrop, 7 links, panel width 351/390, and no horizontal overflow.</x:v>
+      </x:c>
       <x:c r="O19" s="18" t="str"/>
     </x:row>
     <x:row r="20">
@@ -1328,9 +1396,11 @@
       <x:c r="M20" s="29" t="str">
         <x:v>2026-06-29</x:v>
       </x:c>
-      <x:c r="N20" s="26" t="str"/>
+      <x:c r="N20" s="26" t="str">
+        <x:v>Final build verification 2026-06-29: pnpm check/lint/format/build passed; postbuild Pagefind, sitemap, robots, RSS, and manifest assets verified.</x:v>
+      </x:c>
       <x:c r="O20" s="18" t="str">
-        <x:v>Static build passed; browser behavior still needs spot testing.</x:v>
+        <x:v>Article HTML and code rendering verified on the available content fixture.</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1359,7 +1429,7 @@
         <x:v>Open /projects/; verify categories, all six project cards, external links, tag labels, and responsive layout.</x:v>
       </x:c>
       <x:c r="I21" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J21" s="26" t="str">
         <x:v>High</x:v>
@@ -1368,8 +1438,12 @@
       <x:c r="L21" s="26" t="str">
         <x:v>No Fix Needed</x:v>
       </x:c>
-      <x:c r="M21" s="29" t="str"/>
-      <x:c r="N21" s="26" t="str"/>
+      <x:c r="M21" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N21" s="26" t="str">
+        <x:v>/projects/ rendered 12 main links / 13 card-like elements with no overflow.</x:v>
+      </x:c>
       <x:c r="O21" s="18" t="str"/>
     </x:row>
     <x:row r="22">
@@ -1398,7 +1472,7 @@
         <x:v>Open /music/; verify React hydration, layout height, nav overlap, scroll behavior, desktop/mobile behavior, and no console errors.</x:v>
       </x:c>
       <x:c r="I22" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J22" s="26" t="str">
         <x:v>High</x:v>
@@ -1407,8 +1481,12 @@
       <x:c r="L22" s="26" t="str">
         <x:v>No Fix Needed</x:v>
       </x:c>
-      <x:c r="M22" s="29" t="str"/>
-      <x:c r="N22" s="26" t="str"/>
+      <x:c r="M22" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N22" s="26" t="str">
+        <x:v>/music/ hydrated React gallery, rendered visualizer canvas, nav, filters, album list, and no overflow.</x:v>
+      </x:c>
       <x:c r="O22" s="18" t="str"/>
     </x:row>
     <x:row r="23">
@@ -1437,7 +1515,7 @@
         <x:v>Change year/month selects; verify filtered list and empty state; confirm default February 2025 list appears on first load.</x:v>
       </x:c>
       <x:c r="I23" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J23" s="26" t="str">
         <x:v>High</x:v>
@@ -1446,8 +1524,12 @@
       <x:c r="L23" s="26" t="str">
         <x:v>No Fix Needed</x:v>
       </x:c>
-      <x:c r="M23" s="29" t="str"/>
-      <x:c r="N23" s="26" t="str"/>
+      <x:c r="M23" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N23" s="26" t="str">
+        <x:v>Music filters defaulted to February 2025; selecting March showed "No albums found for March 2025".</x:v>
+      </x:c>
       <x:c r="O23" s="18" t="str"/>
     </x:row>
     <x:row r="24">
@@ -1476,7 +1558,7 @@
         <x:v>Click each album; verify highlight, artwork, song title, album, artist, and description update.</x:v>
       </x:c>
       <x:c r="I24" s="26" t="str">
-        <x:v>Needs Browser Verification</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J24" s="26" t="str">
         <x:v>High</x:v>
@@ -1485,12 +1567,16 @@
         <x:v>D005</x:v>
       </x:c>
       <x:c r="L24" s="26" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="M24" s="29" t="str"/>
-      <x:c r="N24" s="26" t="str"/>
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="M24" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N24" s="26" t="str">
+        <x:v>Album rows are keyboard-selectable buttons; pressing Enter selected Eclipse and updated aria-pressed/detail state.</x:v>
+      </x:c>
       <x:c r="O24" s="18" t="str">
-        <x:v>Clickable list entries are divs, not keyboard-focusable buttons.</x:v>
+        <x:v>Fixed by 9293d22.</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1519,7 +1605,7 @@
         <x:v>Verify canvas renders artwork; move pointer; resize viewport; toggle theme; confirm no WebGL/texture errors.</x:v>
       </x:c>
       <x:c r="I25" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J25" s="26" t="str">
         <x:v>High</x:v>
@@ -1528,8 +1614,12 @@
       <x:c r="L25" s="26" t="str">
         <x:v>No Fix Needed</x:v>
       </x:c>
-      <x:c r="M25" s="29" t="str"/>
-      <x:c r="N25" s="26" t="str"/>
+      <x:c r="M25" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N25" s="26" t="str">
+        <x:v>Music page rendered one canvas and album detail state without WebGL/console errors.</x:v>
+      </x:c>
       <x:c r="O25" s="18" t="str"/>
     </x:row>
     <x:row r="26">
@@ -1558,7 +1648,7 @@
         <x:v>Open /changelog/; verify all entries, version badges, dates, links, and responsive layout.</x:v>
       </x:c>
       <x:c r="I26" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J26" s="26" t="str">
         <x:v>Medium</x:v>
@@ -1567,8 +1657,12 @@
       <x:c r="L26" s="26" t="str">
         <x:v>No Fix Needed</x:v>
       </x:c>
-      <x:c r="M26" s="29" t="str"/>
-      <x:c r="N26" s="26" t="str"/>
+      <x:c r="M26" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N26" s="26" t="str">
+        <x:v>/changelog/ rendered 3 changelog links/cards with version/date text and no overflow.</x:v>
+      </x:c>
       <x:c r="O26" s="18" t="str"/>
     </x:row>
     <x:row r="27">
@@ -1597,7 +1691,7 @@
         <x:v>Open each changelog detail; verify version/date/read-time/body/TOC and no console errors.</x:v>
       </x:c>
       <x:c r="I27" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J27" s="26" t="str">
         <x:v>Medium</x:v>
@@ -1606,8 +1700,12 @@
       <x:c r="L27" s="26" t="str">
         <x:v>No Fix Needed</x:v>
       </x:c>
-      <x:c r="M27" s="29" t="str"/>
-      <x:c r="N27" s="26" t="str"/>
+      <x:c r="M27" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N27" s="26" t="str">
+        <x:v>/changelog/0-1-0/, /0-2-0/, and /0-2-1/ all returned 200 with TOC and no overflow/console issues.</x:v>
+      </x:c>
       <x:c r="O27" s="18" t="str"/>
     </x:row>
     <x:row r="28">
@@ -1636,7 +1734,7 @@
         <x:v>Open /feeds/ and /streams/; verify tab labels, active state, links, focus behavior, and responsive layout.</x:v>
       </x:c>
       <x:c r="I28" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J28" s="26" t="str">
         <x:v>Medium</x:v>
@@ -1645,8 +1743,12 @@
       <x:c r="L28" s="26" t="str">
         <x:v>No Fix Needed</x:v>
       </x:c>
-      <x:c r="M28" s="29" t="str"/>
-      <x:c r="N28" s="26" t="str"/>
+      <x:c r="M28" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N28" s="26" t="str">
+        <x:v>/feeds/ and /streams/ rendered tabbed navigation labels Changelog / AstroBlog / AstroStreams.</x:v>
+      </x:c>
       <x:c r="O28" s="18" t="str"/>
     </x:row>
     <x:row r="29">
@@ -1675,7 +1777,7 @@
         <x:v>Open /feeds/; verify feed items, dates, external links, year grouping, TOC, and loader freshness behavior.</x:v>
       </x:c>
       <x:c r="I29" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J29" s="26" t="str">
         <x:v>Medium</x:v>
@@ -1684,10 +1786,14 @@
       <x:c r="L29" s="26" t="str">
         <x:v>No Fix Needed</x:v>
       </x:c>
-      <x:c r="M29" s="29" t="str"/>
-      <x:c r="N29" s="26" t="str"/>
+      <x:c r="M29" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N29" s="26" t="str">
+        <x:v>/feeds/ rendered 196 main links, year grouping, and TOC with no overflow.</x:v>
+      </x:c>
       <x:c r="O29" s="18" t="str">
-        <x:v>External network/cache dependent.</x:v>
+        <x:v>Feed freshness remains upstream-network/cache dependent.</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -1716,7 +1822,7 @@
         <x:v>Open /streams/; verify all stream items, icons, platform labels, external links, and grouping.</x:v>
       </x:c>
       <x:c r="I30" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J30" s="26" t="str">
         <x:v>Low</x:v>
@@ -1725,10 +1831,14 @@
       <x:c r="L30" s="26" t="str">
         <x:v>No Fix Needed</x:v>
       </x:c>
-      <x:c r="M30" s="29" t="str"/>
-      <x:c r="N30" s="26" t="str"/>
+      <x:c r="M30" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N30" s="26" t="str">
+        <x:v>/streams/ rendered 14 main links and grouped stream entries with no overflow.</x:v>
+      </x:c>
       <x:c r="O30" s="18" t="str">
-        <x:v>Currently demo Astro content, not personalized.</x:v>
+        <x:v>Content is still demo Astro stream data.</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -1757,7 +1867,7 @@
         <x:v>Open /releases/ with and without GITHUB_TOKEN; verify cards or clear empty/error state, details expansion, external links, and footer.</x:v>
       </x:c>
       <x:c r="I31" s="26" t="str">
-        <x:v>Defect Open</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J31" s="26" t="str">
         <x:v>Medium</x:v>
@@ -1766,14 +1876,16 @@
         <x:v>D002</x:v>
       </x:c>
       <x:c r="L31" s="26" t="str">
-        <x:v>Open</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="M31" s="29" t="str">
         <x:v>2026-06-29</x:v>
       </x:c>
-      <x:c r="N31" s="26" t="str"/>
+      <x:c r="N31" s="26" t="str">
+        <x:v>/releases/ shows clear optional build-time integration fallback with GITHUB_TOKEN instruction when no token is present.</x:v>
+      </x:c>
       <x:c r="O31" s="18" t="str">
-        <x:v>Build logs token error and generated empty collection.</x:v>
+        <x:v>Fixed by 4efbc6a and copy/template cleanup by ed43d6e.</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -1802,7 +1914,7 @@
         <x:v>Open /prs/ with and without GITHUB_TOKEN; verify cards or clear empty/error state, details expansion, external links, and footer.</x:v>
       </x:c>
       <x:c r="I32" s="26" t="str">
-        <x:v>Defect Open</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J32" s="26" t="str">
         <x:v>Medium</x:v>
@@ -1811,14 +1923,16 @@
         <x:v>D002</x:v>
       </x:c>
       <x:c r="L32" s="26" t="str">
-        <x:v>Open</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="M32" s="29" t="str">
         <x:v>2026-06-29</x:v>
       </x:c>
-      <x:c r="N32" s="26" t="str"/>
+      <x:c r="N32" s="26" t="str">
+        <x:v>/prs/ shows clear optional build-time integration fallback with GITHUB_TOKEN instruction when no token is present.</x:v>
+      </x:c>
       <x:c r="O32" s="18" t="str">
-        <x:v>Build logs token warning and generated empty collection.</x:v>
+        <x:v>Fixed by 4efbc6a and copy/template cleanup by ed43d6e.</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -1847,7 +1961,7 @@
         <x:v>Open /rss.xml; validate XML, feed metadata, item links, date order, and stylesheet link.</x:v>
       </x:c>
       <x:c r="I33" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J33" s="26" t="str">
         <x:v>High</x:v>
@@ -1856,8 +1970,12 @@
       <x:c r="L33" s="26" t="str">
         <x:v>No Fix Needed</x:v>
       </x:c>
-      <x:c r="M33" s="29" t="str"/>
-      <x:c r="N33" s="26" t="str"/>
+      <x:c r="M33" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N33" s="26" t="str">
+        <x:v>/rss.xml returned 200 XML with 1 item and TK site title.</x:v>
+      </x:c>
       <x:c r="O33" s="18" t="str"/>
     </x:row>
     <x:row r="34">
@@ -1886,7 +2004,7 @@
         <x:v>Open manifest; verify JSON, icon URLs, app name/description, theme/background colors.</x:v>
       </x:c>
       <x:c r="I34" s="26" t="str">
-        <x:v>Defect Open</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J34" s="26" t="str">
         <x:v>Low</x:v>
@@ -1895,14 +2013,16 @@
         <x:v>D003</x:v>
       </x:c>
       <x:c r="L34" s="26" t="str">
-        <x:v>Open</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="M34" s="29" t="str">
         <x:v>2026-06-29</x:v>
       </x:c>
-      <x:c r="N34" s="26" t="str"/>
+      <x:c r="N34" s="26" t="str">
+        <x:v>/manifest.webmanifest returned name "TK's Homepage", short_name "TK Home", site description, #0a0a0a theme color, and 3 icons.</x:v>
+      </x:c>
       <x:c r="O34" s="18" t="str">
-        <x:v>Manifest still uses upstream AntfuStyle theme identity, not TK homepage identity.</x:v>
+        <x:v>Fixed by f1aacee.</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -1931,7 +2051,7 @@
         <x:v>Visit missing route; verify 404 page content, layout, nav/back behavior, and HTTP/preview handling.</x:v>
       </x:c>
       <x:c r="I35" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J35" s="26" t="str">
         <x:v>Medium</x:v>
@@ -1940,8 +2060,12 @@
       <x:c r="L35" s="26" t="str">
         <x:v>No Fix Needed</x:v>
       </x:c>
-      <x:c r="M35" s="29" t="str"/>
-      <x:c r="N35" s="26" t="str"/>
+      <x:c r="M35" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N35" s="26" t="str">
+        <x:v>/404.html returns styled 404 page; missing route /not-a-real-route-for-qa-2026 returns HTTP 404 with same styled page.</x:v>
+      </x:c>
       <x:c r="O35" s="18" t="str"/>
     </x:row>
     <x:row r="36">
@@ -1970,7 +2094,7 @@
         <x:v>Find search entry point; click; type query; verify results and panel close behavior on desktop/mobile.</x:v>
       </x:c>
       <x:c r="I36" s="26" t="str">
-        <x:v>Defect Open</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J36" s="26" t="str">
         <x:v>High</x:v>
@@ -1979,14 +2103,16 @@
         <x:v>D001</x:v>
       </x:c>
       <x:c r="L36" s="26" t="str">
-        <x:v>Open</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="M36" s="29" t="str">
         <x:v>2026-06-29</x:v>
       </x:c>
-      <x:c r="N36" s="26" t="str"/>
+      <x:c r="N36" s="26" t="str">
+        <x:v>SEARCH visible in nav; production Pagefind query "server" returned the article result; mobile search panel width 351/390 with backdrop.</x:v>
+      </x:c>
       <x:c r="O36" s="18" t="str">
-        <x:v>Component exists and config expects searchButton, but current NavBar does not mount it.</x:v>
+        <x:v>Fixed by 0623cc8.</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -2015,7 +2141,7 @@
         <x:v>Open article; verify whether share UI appears; if absent, decide if feature should be wired or disabled.</x:v>
       </x:c>
       <x:c r="I37" s="26" t="str">
-        <x:v>Defect Open</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J37" s="26" t="str">
         <x:v>Medium</x:v>
@@ -2024,14 +2150,16 @@
         <x:v>D006</x:v>
       </x:c>
       <x:c r="L37" s="26" t="str">
-        <x:v>Open</x:v>
+        <x:v>Fixed</x:v>
       </x:c>
       <x:c r="M37" s="29" t="str">
         <x:v>2026-06-29</x:v>
       </x:c>
-      <x:c r="N37" s="26" t="str"/>
+      <x:c r="N37" s="26" t="str">
+        <x:v>Article renders Twitter share link to twitter.com/intent/tweet using the canonical article URL.</x:v>
+      </x:c>
       <x:c r="O37" s="18" t="str">
-        <x:v>Configured/enabled feature is currently unreachable in rendered pages.</x:v>
+        <x:v>Fixed by af7553f.</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -2060,7 +2188,7 @@
         <x:v>Visit dot/plum pages; inspect background layering, no pointer interference, no console errors, light/dark contrast.</x:v>
       </x:c>
       <x:c r="I38" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J38" s="26" t="str">
         <x:v>Medium</x:v>
@@ -2069,10 +2197,14 @@
       <x:c r="L38" s="26" t="str">
         <x:v>No Fix Needed</x:v>
       </x:c>
-      <x:c r="M38" s="29" t="str"/>
-      <x:c r="N38" s="26" t="str"/>
+      <x:c r="M38" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N38" s="26" t="str">
+        <x:v>Pages with bgType/backgrounds rendered without pointer interference, overflow, or console warning/error in production preview.</x:v>
+      </x:c>
       <x:c r="O38" s="18" t="str">
-        <x:v>Rose/Particle exist but may not be used by current public pages.</x:v>
+        <x:v>Rose/Particle remain available but are not used by current public routes.</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -2113,10 +2245,10 @@
       <x:c r="M39" s="29" t="str">
         <x:v>2026-06-29</x:v>
       </x:c>
-      <x:c r="N39" s="26" t="str"/>
-      <x:c r="O39" s="18" t="str">
-        <x:v>Build indexed 4 pages and 336 words.</x:v>
-      </x:c>
+      <x:c r="N39" s="26" t="str">
+        <x:v>pnpm build ran Pagefind successfully: 4 pages indexed, 335 words, output in dist/pagefind.</x:v>
+      </x:c>
+      <x:c r="O39" s="18" t="str"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="17" t="str">
@@ -2156,10 +2288,10 @@
       <x:c r="M40" s="29" t="str">
         <x:v>2026-06-29</x:v>
       </x:c>
-      <x:c r="N40" s="26" t="str"/>
-      <x:c r="O40" s="18" t="str">
-        <x:v>Build generated sitemap-index.xml and robots.txt.</x:v>
-      </x:c>
+      <x:c r="N40" s="26" t="str">
+        <x:v>pnpm build generated dist/sitemap-index.xml and dist/robots.txt.</x:v>
+      </x:c>
+      <x:c r="O40" s="18" t="str"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="17" t="str">
@@ -2199,10 +2331,10 @@
       <x:c r="M41" s="29" t="str">
         <x:v>2026-06-29</x:v>
       </x:c>
-      <x:c r="N41" s="26" t="str"/>
-      <x:c r="O41" s="18" t="str">
-        <x:v>astro check passed with 0 diagnostics.</x:v>
-      </x:c>
+      <x:c r="N41" s="26" t="str">
+        <x:v>pnpm check reported 0 errors, 0 warnings, 0 hints across 72 files.</x:v>
+      </x:c>
+      <x:c r="O41" s="18" t="str"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="17" t="str">
@@ -2242,9 +2374,11 @@
       <x:c r="M42" s="29" t="str">
         <x:v>2026-06-29</x:v>
       </x:c>
-      <x:c r="N42" s="26" t="str"/>
+      <x:c r="N42" s="26" t="str">
+        <x:v>Production build completed with OG image generation pipeline enabled and no plugin errors.</x:v>
+      </x:c>
       <x:c r="O42" s="18" t="str">
-        <x:v>Needs browser/meta spot verification.</x:v>
+        <x:v>Article metadata spot-checked during route regression.</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -2273,7 +2407,7 @@
         <x:v>Verify which components are actually reachable; remove, wire, or mark intentionally unused.</x:v>
       </x:c>
       <x:c r="I43" s="26" t="str">
-        <x:v>Defect Open</x:v>
+        <x:v>Deferred</x:v>
       </x:c>
       <x:c r="J43" s="26" t="str">
         <x:v>Low</x:v>
@@ -2282,14 +2416,16 @@
         <x:v>D007</x:v>
       </x:c>
       <x:c r="L43" s="26" t="str">
-        <x:v>Open</x:v>
+        <x:v>Deferred</x:v>
       </x:c>
       <x:c r="M43" s="29" t="str">
         <x:v>2026-06-29</x:v>
       </x:c>
-      <x:c r="N43" s="26" t="str"/>
+      <x:c r="N43" s="26" t="str">
+        <x:v>Custom NavBar now exposes the intended public nav/search/theme behavior; remaining unused upstream widgets have no current visitor-visible impact.</x:v>
+      </x:c>
       <x:c r="O43" s="18" t="str">
-        <x:v>Several upstream widgets remain present but unused after custom NavBar.</x:v>
+        <x:v>Maintenance backlog only; not a UX/logistical release blocker.</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -2318,19 +2454,23 @@
         <x:v>Crawl visible links; verify internal 200s, external targets, new tab behavior where intended, and no broken /blog customizer link.</x:v>
       </x:c>
       <x:c r="I44" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J44" s="26" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="K44" s="26" t="str"/>
       <x:c r="L44" s="26" t="str">
-        <x:v>No Fix Needed</x:v>
-      </x:c>
-      <x:c r="M44" s="29" t="str"/>
-      <x:c r="N44" s="26" t="str"/>
+        <x:v>Fixed</x:v>
+      </x:c>
+      <x:c r="M44" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N44" s="26" t="str">
+        <x:v>Static crawl checked 302 local href/src refs across 14 HTML files with 0 broken refs.</x:v>
+      </x:c>
       <x:c r="O44" s="18" t="str">
-        <x:v>GithubView footer links to a blog article not present in current content; browser crawl will confirm behavior.</x:v>
+        <x:v>Broken GitHub activity config link/template copy fixed by ed43d6e.</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -2359,7 +2499,7 @@
         <x:v>Test 390x844 and 375x812 across core routes; verify no horizontal overflow, clipped controls, or unreachable content.</x:v>
       </x:c>
       <x:c r="I45" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J45" s="26" t="str">
         <x:v>High</x:v>
@@ -2368,8 +2508,12 @@
       <x:c r="L45" s="26" t="str">
         <x:v>No Fix Needed</x:v>
       </x:c>
-      <x:c r="M45" s="29" t="str"/>
-      <x:c r="N45" s="26" t="str"/>
+      <x:c r="M45" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N45" s="26" t="str">
+        <x:v>390x844 mobile checks passed for home, search overlay, TOC overlay, and core routes with no horizontal overflow.</x:v>
+      </x:c>
       <x:c r="O45" s="18" t="str"/>
     </x:row>
     <x:row r="46">
@@ -2398,7 +2542,7 @@
         <x:v>Inspect production build/page source; verify analytics script loads only as expected and causes no console errors.</x:v>
       </x:c>
       <x:c r="I46" s="26" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="J46" s="26" t="str">
         <x:v>Low</x:v>
@@ -2407,8 +2551,12 @@
       <x:c r="L46" s="26" t="str">
         <x:v>No Fix Needed</x:v>
       </x:c>
-      <x:c r="M46" s="29" t="str"/>
-      <x:c r="N46" s="26" t="str"/>
+      <x:c r="M46" s="29" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+      <x:c r="N46" s="26" t="str">
+        <x:v>Vercel analytics inclusion produced only expected local-development log; final route regression found no warning/error console entries.</x:v>
+      </x:c>
       <x:c r="O46" s="18" t="str"/>
     </x:row>
     <x:row r="47">
@@ -2449,10 +2597,10 @@
       <x:c r="M47" s="30" t="str">
         <x:v>2026-06-29</x:v>
       </x:c>
-      <x:c r="N47" s="27" t="str"/>
-      <x:c r="O47" s="20" t="str">
-        <x:v>Local check/lint/format/build passed.</x:v>
-      </x:c>
+      <x:c r="N47" s="27" t="str">
+        <x:v>Local CI equivalent passed: pnpm check; pnpm lint; pnpm format; pnpm build.</x:v>
+      </x:c>
+      <x:c r="O47" s="20" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -2472,7 +2620,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52302bb137ee4e35"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0dea4b07f70c4e8b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2504,7 +2652,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="4" t="str">
-        <x:v>Open issues discovered from source/build inventory. Browser QA will attach screenshots/evidence and confirm/fix each issue.</x:v>
+        <x:v>Defects discovered during source/build/browser QA. User-visible issues are verified fixed; D007 is deferred as non-user-visible maintenance backlog.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -2565,7 +2713,7 @@
         <x:v>UX / Functional</x:v>
       </x:c>
       <x:c r="E5" s="25" t="str">
-        <x:v>Open</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="F5" s="25" t="str">
         <x:v>src/config.ts; src/components/base/NavBar.astro; src/components/widgets/SearchSwitch.astro</x:v>
@@ -2580,13 +2728,17 @@
         <x:v>No visible search entry point is expected in current rendered navigation.</x:v>
       </x:c>
       <x:c r="J5" s="25" t="str">
-        <x:v>Code inventory; pending browser screenshot.</x:v>
+        <x:v>Production preview search opened from nav; Pagefind query "server" returned 1 article result; mobile search panel fit 351/390 with backdrop.</x:v>
       </x:c>
       <x:c r="K5" s="25" t="str">
         <x:v>Wire SearchSwitch into NavBar or disable/remove search config intentionally.</x:v>
       </x:c>
-      <x:c r="L5" s="25" t="str"/>
-      <x:c r="M5" s="25" t="str"/>
+      <x:c r="L5" s="25" t="str">
+        <x:v>0623cc8</x:v>
+      </x:c>
+      <x:c r="M5" s="25" t="str">
+        <x:v>Passed — search is visible and functional on desktop/mobile.</x:v>
+      </x:c>
       <x:c r="N5" s="31" t="str">
         <x:v>2026-06-29</x:v>
       </x:c>
@@ -2605,7 +2757,7 @@
         <x:v>Data / Build</x:v>
       </x:c>
       <x:c r="E6" s="26" t="str">
-        <x:v>Open</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="F6" s="26" t="str">
         <x:v>src/content/config.ts; production build output</x:v>
@@ -2620,13 +2772,17 @@
         <x:v>/releases/ and /prs/ are routable but likely render empty activity lists with only footer content.</x:v>
       </x:c>
       <x:c r="J6" s="26" t="str">
-        <x:v>pnpm check/build 2026-06-29.</x:v>
+        <x:v>pnpm check/build no longer emit GitHub token loader warnings/errors; /releases/ and /prs/ show GITHUB_TOKEN fallback copy without AstroEco text.</x:v>
       </x:c>
       <x:c r="K6" s="26" t="str">
         <x:v>Add resilient empty state and/or make token requirement explicit; consider hiding demo routes from nav/sitemap.</x:v>
       </x:c>
-      <x:c r="L6" s="26" t="str"/>
-      <x:c r="M6" s="26" t="str"/>
+      <x:c r="L6" s="26" t="str">
+        <x:v>4efbc6a</x:v>
+      </x:c>
+      <x:c r="M6" s="26" t="str">
+        <x:v>Passed — optional no-token state is explicit and build-clean.</x:v>
+      </x:c>
       <x:c r="N6" s="32" t="str">
         <x:v>2026-06-29</x:v>
       </x:c>
@@ -2645,7 +2801,7 @@
         <x:v>Content / Branding</x:v>
       </x:c>
       <x:c r="E7" s="26" t="str">
-        <x:v>Open</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="F7" s="26" t="str">
         <x:v>src/pages/manifest.webmanifest.js</x:v>
@@ -2660,13 +2816,17 @@
         <x:v>Installed app/search previews would show upstream theme branding.</x:v>
       </x:c>
       <x:c r="J7" s="26" t="str">
-        <x:v>Code inventory.</x:v>
+        <x:v>/manifest.webmanifest returns TK's Homepage / TK Home / current SITE description / #0a0a0a.</x:v>
       </x:c>
       <x:c r="K7" s="26" t="str">
         <x:v>Update manifest name, short_name, description, and colors to match SITE config.</x:v>
       </x:c>
-      <x:c r="L7" s="26" t="str"/>
-      <x:c r="M7" s="26" t="str"/>
+      <x:c r="L7" s="26" t="str">
+        <x:v>f1aacee</x:v>
+      </x:c>
+      <x:c r="M7" s="26" t="str">
+        <x:v>Passed — manifest identity matches site identity.</x:v>
+      </x:c>
       <x:c r="N7" s="32" t="str">
         <x:v>2026-06-29</x:v>
       </x:c>
@@ -2685,7 +2845,7 @@
         <x:v>UX / Navigation</x:v>
       </x:c>
       <x:c r="E8" s="26" t="str">
-        <x:v>Open</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="F8" s="26" t="str">
         <x:v>src/config.ts; src/components/base/NavBar.astro; src/pages/index.mdx</x:v>
@@ -2700,13 +2860,17 @@
         <x:v>Music and Changelog are not reachable from the visible nav; homepage has no visible internal content navigation.</x:v>
       </x:c>
       <x:c r="J8" s="26" t="str">
-        <x:v>Code inventory; pending browser verification.</x:v>
+        <x:v>Home nav exposes BLOG/PROJECTS/MUSIC/SEARCH; internal nav exposes BLOG/PROJECTS/MUSIC/CHANGELOG/SEARCH.</x:v>
       </x:c>
       <x:c r="K8" s="26" t="str">
         <x:v>Adjust NavBar/homepage navigation to expose the intended core sections while preserving the homepage visual style.</x:v>
       </x:c>
-      <x:c r="L8" s="26" t="str"/>
-      <x:c r="M8" s="26" t="str"/>
+      <x:c r="L8" s="26" t="str">
+        <x:v>0623cc8</x:v>
+      </x:c>
+      <x:c r="M8" s="26" t="str">
+        <x:v>Passed — core sections are discoverable while homepage style is preserved.</x:v>
+      </x:c>
       <x:c r="N8" s="32" t="str">
         <x:v>2026-06-29</x:v>
       </x:c>
@@ -2725,7 +2889,7 @@
         <x:v>Accessibility</x:v>
       </x:c>
       <x:c r="E9" s="26" t="str">
-        <x:v>Open</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="F9" s="26" t="str">
         <x:v>src/components/music/AlbumList.jsx</x:v>
@@ -2740,13 +2904,17 @@
         <x:v>Mouse users can select albums; keyboard users likely cannot.</x:v>
       </x:c>
       <x:c r="J9" s="26" t="str">
-        <x:v>Code inventory; pending browser verification.</x:v>
+        <x:v>Album rows render as buttons with aria-pressed; Enter selected Eclipse and updated detail state.</x:v>
       </x:c>
       <x:c r="K9" s="26" t="str">
         <x:v>Render album entries as buttons or add equivalent keyboard/ARIA semantics.</x:v>
       </x:c>
-      <x:c r="L9" s="26" t="str"/>
-      <x:c r="M9" s="26" t="str"/>
+      <x:c r="L9" s="26" t="str">
+        <x:v>9293d22</x:v>
+      </x:c>
+      <x:c r="M9" s="26" t="str">
+        <x:v>Passed — album selection is keyboard-operable.</x:v>
+      </x:c>
       <x:c r="N9" s="32" t="str">
         <x:v>2026-06-29</x:v>
       </x:c>
@@ -2765,7 +2933,7 @@
         <x:v>Functional / Configuration</x:v>
       </x:c>
       <x:c r="E10" s="26" t="str">
-        <x:v>Open</x:v>
+        <x:v>Verified</x:v>
       </x:c>
       <x:c r="F10" s="26" t="str">
         <x:v>src/config.ts; src/components/widgets/ShareLink.astro; src/layouts/BaseLayout.astro</x:v>
@@ -2780,54 +2948,192 @@
         <x:v>Share UI appears unreachable from current article route.</x:v>
       </x:c>
       <x:c r="J10" s="26" t="str">
-        <x:v>Code inventory; pending browser verification.</x:v>
+        <x:v>Article route renders Twitter share link to twitter.com/intent/tweet with canonical article URL.</x:v>
       </x:c>
       <x:c r="K10" s="26" t="str">
         <x:v>Wire ShareLink into article pages when frontmatter.share is true, or disable share config.</x:v>
       </x:c>
-      <x:c r="L10" s="26" t="str"/>
-      <x:c r="M10" s="26" t="str"/>
+      <x:c r="L10" s="26" t="str">
+        <x:v>af7553f</x:v>
+      </x:c>
+      <x:c r="M10" s="26" t="str">
+        <x:v>Passed — enabled share feature is reachable on article pages.</x:v>
+      </x:c>
       <x:c r="N10" s="32" t="str">
         <x:v>2026-06-29</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="19" t="str">
+      <x:c r="A11" s="17" t="str">
         <x:v>D007</x:v>
       </x:c>
-      <x:c r="B11" s="27" t="str">
+      <x:c r="B11" s="26" t="str">
         <x:v>F039</x:v>
       </x:c>
-      <x:c r="C11" s="27" t="str">
+      <x:c r="C11" s="26" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="D11" s="27" t="str">
+      <x:c r="D11" s="26" t="str">
         <x:v>Maintainability / UX</x:v>
       </x:c>
-      <x:c r="E11" s="27" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="F11" s="27" t="str">
+      <x:c r="E11" s="26" t="str">
+        <x:v>Deferred</x:v>
+      </x:c>
+      <x:c r="F11" s="26" t="str">
         <x:v>src/components/widgets/NavSwitch.astro; RssLink.astro; LogoButton.astro; src/components/base/NavItem.astro</x:v>
       </x:c>
-      <x:c r="G11" s="27" t="str">
+      <x:c r="G11" s="26" t="str">
         <x:v>Several upstream navigation widgets remain present but are no longer used by the custom NavBar.</x:v>
       </x:c>
-      <x:c r="H11" s="27" t="str">
+      <x:c r="H11" s="26" t="str">
         <x:v>Reusable widgets should either be intentionally wired, documented as legacy, or removed to reduce confusion.</x:v>
       </x:c>
-      <x:c r="I11" s="27" t="str">
+      <x:c r="I11" s="26" t="str">
         <x:v>Config and implementation can drift, making future UX changes error-prone.</x:v>
       </x:c>
-      <x:c r="J11" s="27" t="str">
-        <x:v>Code inventory.</x:v>
-      </x:c>
-      <x:c r="K11" s="27" t="str">
+      <x:c r="J11" s="26" t="str">
+        <x:v>Post-fix public nav/search/theme behavior is verified; unused upstream widgets do not affect current visitors.</x:v>
+      </x:c>
+      <x:c r="K11" s="26" t="str">
         <x:v>Decide whether to restore config-driven NavBar or remove unused upstream widgets.</x:v>
       </x:c>
-      <x:c r="L11" s="27" t="str"/>
-      <x:c r="M11" s="27" t="str"/>
-      <x:c r="N11" s="33" t="str">
+      <x:c r="L11" s="26" t="str"/>
+      <x:c r="M11" s="26" t="str">
+        <x:v>Deferred — maintenance cleanup only, not a user-visible UX/logistical blocker.</x:v>
+      </x:c>
+      <x:c r="N11" s="32" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="17" t="str">
+        <x:v>D008</x:v>
+      </x:c>
+      <x:c r="B12" s="26" t="str">
+        <x:v>F012</x:v>
+      </x:c>
+      <x:c r="C12" s="26" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="D12" s="26" t="str">
+        <x:v>UX / Layout</x:v>
+      </x:c>
+      <x:c r="E12" s="26" t="str">
+        <x:v>Verified</x:v>
+      </x:c>
+      <x:c r="F12" s="26" t="str">
+        <x:v>src/pages/index.mdx</x:v>
+      </x:c>
+      <x:c r="G12" s="26" t="str">
+        <x:v>Homepage used React-style className attributes in Astro markup, so layout classes were not applied reliably.</x:v>
+      </x:c>
+      <x:c r="H12" s="26" t="str">
+        <x:v>Homepage should render the intended three-column editorial grid on desktop and one-column stack on mobile.</x:v>
+      </x:c>
+      <x:c r="I12" s="26" t="str">
+        <x:v>Desktop homepage layout could collapse/lose intended styling.</x:v>
+      </x:c>
+      <x:c r="J12" s="26" t="str">
+        <x:v>Browser regression: 1280px grid columns 384px / 384px / 384px; mobile 390px no overflow.</x:v>
+      </x:c>
+      <x:c r="K12" s="26" t="str">
+        <x:v>Replace className with class in Astro page markup.</x:v>
+      </x:c>
+      <x:c r="L12" s="26" t="str">
+        <x:v>8e2c78a</x:v>
+      </x:c>
+      <x:c r="M12" s="26" t="str">
+        <x:v>Passed — homepage layout restored and responsive.</x:v>
+      </x:c>
+      <x:c r="N12" s="32" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="17" t="str">
+        <x:v>D009</x:v>
+      </x:c>
+      <x:c r="B13" s="26" t="str">
+        <x:v>F027; F028; F040</x:v>
+      </x:c>
+      <x:c r="C13" s="26" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="D13" s="26" t="str">
+        <x:v>Content / Link Integrity</x:v>
+      </x:c>
+      <x:c r="E13" s="26" t="str">
+        <x:v>Verified</x:v>
+      </x:c>
+      <x:c r="F13" s="26" t="str">
+        <x:v>src/components/views/GithubView.astro; src/pages/releases.mdx; src/pages/prs.mdx</x:v>
+      </x:c>
+      <x:c r="G13" s="26" t="str">
+        <x:v>GitHub activity pages retained upstream/template copy and linked to a missing local configuration article.</x:v>
+      </x:c>
+      <x:c r="H13" s="26" t="str">
+        <x:v>Optional GitHub pages should use neutral TK-site copy and only link to valid resources.</x:v>
+      </x:c>
+      <x:c r="I13" s="26" t="str">
+        <x:v>Visitors could see stale AstroEco wording or hit a broken /blog/customizing-github-activity-pages/ URL.</x:v>
+      </x:c>
+      <x:c r="J13" s="26" t="str">
+        <x:v>Static crawl: 14 HTML files / 302 refs / 0 broken; releases/prs contain no AstroEco text.</x:v>
+      </x:c>
+      <x:c r="K13" s="26" t="str">
+        <x:v>Replace stale local link with astro-loaders docs and update page titles/descriptions.</x:v>
+      </x:c>
+      <x:c r="L13" s="26" t="str">
+        <x:v>ed43d6e</x:v>
+      </x:c>
+      <x:c r="M13" s="26" t="str">
+        <x:v>Passed — no broken local refs and no AstroEco copy.</x:v>
+      </x:c>
+      <x:c r="N13" s="32" t="str">
+        <x:v>2026-06-29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="19" t="str">
+        <x:v>D010</x:v>
+      </x:c>
+      <x:c r="B14" s="27" t="str">
+        <x:v>F014</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="str">
+        <x:v>Low</x:v>
+      </x:c>
+      <x:c r="D14" s="27" t="str">
+        <x:v>Content / Copy</x:v>
+      </x:c>
+      <x:c r="E14" s="27" t="str">
+        <x:v>Verified</x:v>
+      </x:c>
+      <x:c r="F14" s="27" t="str">
+        <x:v>src/content/blog/about-open-graph-images.md</x:v>
+      </x:c>
+      <x:c r="G14" s="27" t="str">
+        <x:v>Public article contained awkward/incorrect wording such as "enviroment" and "via appimage".</x:v>
+      </x:c>
+      <x:c r="H14" s="27" t="str">
+        <x:v>Public writing should be clean enough for collaborators and general visitors.</x:v>
+      </x:c>
+      <x:c r="I14" s="27" t="str">
+        <x:v>Article copy had visible typos and rough phrasing.</x:v>
+      </x:c>
+      <x:c r="J14" s="27" t="str">
+        <x:v>Article route rendered cleaned copy in production preview with no console issues.</x:v>
+      </x:c>
+      <x:c r="K14" s="27" t="str">
+        <x:v>Edit article copy while preserving technical meaning.</x:v>
+      </x:c>
+      <x:c r="L14" s="27" t="str">
+        <x:v>30d3343</x:v>
+      </x:c>
+      <x:c r="M14" s="27" t="str">
+        <x:v>Passed — public copy cleaned.</x:v>
+      </x:c>
+      <x:c r="N14" s="33" t="str">
         <x:v>2026-06-29</x:v>
       </x:c>
     </x:row>
@@ -2837,16 +3143,16 @@
     <x:mergeCell ref="A2:N2"/>
   </x:mergeCells>
   <x:dataValidations count="2">
-    <x:dataValidation type="list" sqref="C5:C11">
+    <x:dataValidation type="list" sqref="C5:C14">
       <x:formula1>"Critical,High,Medium,Low,Cosmetic"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="E5:E11">
+    <x:dataValidation type="list" sqref="E5:E14">
       <x:formula1>"Open,Fixed,Retest Pending,Verified,Deferred"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c699acffb314702"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d37563308244fc2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2871,7 +3177,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="4" t="str">
-        <x:v>Chronological evidence log. Browser screenshots and final pass/fail status will be appended here as QA progresses.</x:v>
+        <x:v>Chronological evidence log for inventory, baseline, fix loop, and final production-preview regression.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -2944,26 +3250,95 @@
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="19" t="str">
+      <x:c r="A7" s="17" t="str">
         <x:v>TR003</x:v>
       </x:c>
-      <x:c r="B7" s="30" t="n">
+      <x:c r="B7" s="29" t="n">
         <x:v>46202</x:v>
       </x:c>
-      <x:c r="C7" s="27" t="str">
+      <x:c r="C7" s="26" t="str">
         <x:v>Baseline commit</x:v>
       </x:c>
-      <x:c r="D7" s="27" t="str">
+      <x:c r="D7" s="26" t="str">
         <x:v>Previous style/config migration</x:v>
       </x:c>
-      <x:c r="E7" s="27" t="str">
+      <x:c r="E7" s="26" t="str">
         <x:v>git commit 05cdd87</x:v>
       </x:c>
-      <x:c r="F7" s="27" t="str">
+      <x:c r="F7" s="26" t="str">
         <x:v>Complete</x:v>
       </x:c>
-      <x:c r="G7" s="20" t="str">
+      <x:c r="G7" s="18" t="str">
         <x:v>Clean QA baseline before formal browser test/fix loop.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="17" t="str">
+        <x:v>TR004</x:v>
+      </x:c>
+      <x:c r="B8" s="29" t="n">
+        <x:v>46202</x:v>
+      </x:c>
+      <x:c r="C8" s="26" t="str">
+        <x:v>Browser baseline</x:v>
+      </x:c>
+      <x:c r="D8" s="26" t="str">
+        <x:v>Core public routes and interactions</x:v>
+      </x:c>
+      <x:c r="E8" s="26" t="str">
+        <x:v>In-app browser on local dev/preview; screenshots in .gstack/qa-reports/screenshots</x:v>
+      </x:c>
+      <x:c r="F8" s="26" t="str">
+        <x:v>Failed with defects</x:v>
+      </x:c>
+      <x:c r="G8" s="18" t="str">
+        <x:v>Found homepage layout issue, hidden/unwired search/nav, manifest branding, music keyboard accessibility, GitHub optional-state issues, missing article share links, stale GitHub copy/link, and article copy issues.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="17" t="str">
+        <x:v>TR005</x:v>
+      </x:c>
+      <x:c r="B9" s="29" t="n">
+        <x:v>46202</x:v>
+      </x:c>
+      <x:c r="C9" s="26" t="str">
+        <x:v>Fix loop</x:v>
+      </x:c>
+      <x:c r="D9" s="26" t="str">
+        <x:v>D001-D006, D008-D010</x:v>
+      </x:c>
+      <x:c r="E9" s="26" t="str">
+        <x:v>Commits 8e2c78a, 0623cc8, f1aacee, 9293d22, 4efbc6a, af7553f, ed43d6e, 30d3343</x:v>
+      </x:c>
+      <x:c r="F9" s="26" t="str">
+        <x:v>Complete</x:v>
+      </x:c>
+      <x:c r="G9" s="18" t="str">
+        <x:v>One focused fix per issue class; .gstack QA evidence kept local and ignored.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="19" t="str">
+        <x:v>TR006</x:v>
+      </x:c>
+      <x:c r="B10" s="30" t="n">
+        <x:v>46202</x:v>
+      </x:c>
+      <x:c r="C10" s="27" t="str">
+        <x:v>Final regression</x:v>
+      </x:c>
+      <x:c r="D10" s="27" t="str">
+        <x:v>All 43 user stories, 15 route states, desktop/mobile overlays, production search, manifest, RSS, links, build checks</x:v>
+      </x:c>
+      <x:c r="E10" s="27" t="str">
+        <x:v>pnpm check; pnpm lint; pnpm format; pnpm build; production preview http://127.0.0.1:4322; internal link crawl</x:v>
+      </x:c>
+      <x:c r="F10" s="27" t="str">
+        <x:v>Passed</x:v>
+      </x:c>
+      <x:c r="G10" s="20" t="str">
+        <x:v>0 Astro diagnostics, 0 lint/format failures, build passed, 0 broken local refs, 0 console warning/error route regressions, all user-visible defects retested fixed.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2973,7 +3348,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb37375509a64328"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79497c91331149a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3171,10 +3546,10 @@
         <x:v>Known build concern</x:v>
       </x:c>
       <x:c r="B16" s="26" t="str">
-        <x:v>GitHub token required for releases/prs loaders</x:v>
+        <x:v>GitHub token optional for releases/prs loaders</x:v>
       </x:c>
       <x:c r="C16" s="26" t="str">
-        <x:v>See D002.</x:v>
+        <x:v>No-token builds show fallback copy.</x:v>
       </x:c>
       <x:c r="D16" s="18" t="str">
         <x:v>Codex</x:v>
@@ -3185,10 +3560,10 @@
         <x:v>Next update</x:v>
       </x:c>
       <x:c r="B17" s="27" t="str">
-        <x:v>Append browser QA evidence</x:v>
+        <x:v>Append deployment evidence if shipped</x:v>
       </x:c>
       <x:c r="C17" s="27" t="str">
-        <x:v>After local preview test pass.</x:v>
+        <x:v>After production deploy/canary.</x:v>
       </x:c>
       <x:c r="D17" s="20" t="str">
         <x:v>Codex</x:v>
